--- a/phase-1/TOPSIS.xlsx
+++ b/phase-1/TOPSIS.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Home\labs\project-management\phase-1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6776008-8A5F-4006-82EB-492276D3DB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Главная" sheetId="1" r:id="rId1"/>
+    <sheet name="Оценки" sheetId="2" r:id="rId2"/>
+    <sheet name="TOPSIS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,9 +26,185 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="57">
+  <si>
+    <t>Э1</t>
+  </si>
+  <si>
+    <t>Э2</t>
+  </si>
+  <si>
+    <t>Э3</t>
+  </si>
+  <si>
+    <t>Условное обозначение</t>
+  </si>
+  <si>
+    <t>Эксперт</t>
+  </si>
+  <si>
+    <t>Манойленко Андрей</t>
+  </si>
+  <si>
+    <t>Токарев Артем</t>
+  </si>
+  <si>
+    <t>Алпутов Данил</t>
+  </si>
+  <si>
+    <t>УО</t>
+  </si>
+  <si>
+    <t>Критерий</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Востребованность продукта (спрос) на рынке</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>Трудоемкость разработки (ресурсы, исполнители)</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Возможность монетизации</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Зависимость от стороннего технического обеспечения</t>
+  </si>
+  <si>
+    <t>Пессимистичная</t>
+  </si>
+  <si>
+    <t>Ожидаемая</t>
+  </si>
+  <si>
+    <t>Оптимистичная</t>
+  </si>
+  <si>
+    <t>Тип</t>
+  </si>
+  <si>
+    <t>Выгода</t>
+  </si>
+  <si>
+    <t>Затраты</t>
+  </si>
+  <si>
+    <t>Пояснение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выгода </t>
+  </si>
+  <si>
+    <t>То что нужно максимизировать (это ведь не очевидно да?)</t>
+  </si>
+  <si>
+    <t>То что нужно минимизировать (тоже не очевидно)</t>
+  </si>
+  <si>
+    <t>Бальная шкала</t>
+  </si>
+  <si>
+    <t>Балл</t>
+  </si>
+  <si>
+    <t>Средний(ая)</t>
+  </si>
+  <si>
+    <t>Уо</t>
+  </si>
+  <si>
+    <t>Альтернатива</t>
+  </si>
+  <si>
+    <t>А1</t>
+  </si>
+  <si>
+    <t>А2</t>
+  </si>
+  <si>
+    <t>А3</t>
+  </si>
+  <si>
+    <t>А4</t>
+  </si>
+  <si>
+    <t>Мобильное приложение с геймификацией для обучения финансовой грамотности и контролю трат</t>
+  </si>
+  <si>
+    <t>ИИ ассистент по финансам</t>
+  </si>
+  <si>
+    <t>Облачный сервис для совместного ведения конспектов и проектов студентами группы</t>
+  </si>
+  <si>
+    <t>Приложение для практики речи на иностранном языке с ИИ учителем</t>
+  </si>
+  <si>
+    <t>А5</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>С1</t>
+  </si>
+  <si>
+    <t>С2</t>
+  </si>
+  <si>
+    <t>С3</t>
+  </si>
+  <si>
+    <t>С4</t>
+  </si>
+  <si>
+    <t>Маленький(ая)</t>
+  </si>
+  <si>
+    <t>Очень низкий(ая)</t>
+  </si>
+  <si>
+    <t>Большой(ая)</t>
+  </si>
+  <si>
+    <t>Очень высокий(ая)</t>
+  </si>
+  <si>
+    <t>Плюсом промежуточные значения как среднее между этим пояснением</t>
+  </si>
+  <si>
+    <t>Приложение для ручного/автоматического учета ежедневных расходов и доходов</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +212,59 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,15 +272,84 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF3D444D"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF3D444D"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF3D444D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF3D444D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="20% — акцент1" xfId="2" builtinId="30"/>
+    <cellStyle name="40% — акцент1" xfId="3" builtinId="31"/>
+    <cellStyle name="60% — акцент1" xfId="4" builtinId="32"/>
+    <cellStyle name="Гиперссылка" xfId="5" builtinId="8"/>
+    <cellStyle name="Заголовок 4" xfId="1" builtinId="19"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,9 +626,1060 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" customWidth="1"/>
+    <col min="7" max="7" width="77.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C6A046-B866-473F-A073-A909A54E0887}">
+  <dimension ref="A1:N42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <v>5</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
+        <v>7</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="13">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13">
+        <v>4</v>
+      </c>
+      <c r="D14" s="13">
+        <v>6</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="K14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="13">
+        <v>3</v>
+      </c>
+      <c r="C15" s="13">
+        <v>6</v>
+      </c>
+      <c r="D15" s="13">
+        <v>7</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="K15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="13">
+        <v>5</v>
+      </c>
+      <c r="C16" s="13">
+        <v>7</v>
+      </c>
+      <c r="D16" s="13">
+        <v>9</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="K16" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="13">
+        <v>6</v>
+      </c>
+      <c r="C17" s="13">
+        <v>7</v>
+      </c>
+      <c r="D17" s="13">
+        <v>9</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="K17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="13">
+        <v>6</v>
+      </c>
+      <c r="C18" s="13">
+        <v>8</v>
+      </c>
+      <c r="D18" s="13">
+        <v>9</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="K18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="13">
+        <v>8</v>
+      </c>
+      <c r="C22" s="13">
+        <v>5</v>
+      </c>
+      <c r="D22" s="13">
+        <v>4</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="K22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="13">
+        <v>5</v>
+      </c>
+      <c r="C23" s="13">
+        <v>3</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="K23" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="13">
+        <v>9</v>
+      </c>
+      <c r="C24" s="13">
+        <v>6</v>
+      </c>
+      <c r="D24" s="13">
+        <v>4</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="K24" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="13">
+        <v>8</v>
+      </c>
+      <c r="C25" s="13">
+        <v>6</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="K25" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="13">
+        <v>6</v>
+      </c>
+      <c r="C26" s="13">
+        <v>3</v>
+      </c>
+      <c r="D26" s="13">
+        <v>1</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="K26" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="13">
+        <v>3</v>
+      </c>
+      <c r="C30" s="13">
+        <v>4</v>
+      </c>
+      <c r="D30" s="13">
+        <v>5</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="K30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="13">
+        <v>1</v>
+      </c>
+      <c r="C31" s="13">
+        <v>3</v>
+      </c>
+      <c r="D31" s="13">
+        <v>5</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="K31" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="13">
+        <v>4</v>
+      </c>
+      <c r="C32" s="13">
+        <v>6</v>
+      </c>
+      <c r="D32" s="13">
+        <v>7</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="K32" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="13">
+        <v>4</v>
+      </c>
+      <c r="C33" s="13">
+        <v>7</v>
+      </c>
+      <c r="D33" s="13">
+        <v>9</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="K33" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="13">
+        <v>5</v>
+      </c>
+      <c r="C34" s="13">
+        <v>8</v>
+      </c>
+      <c r="D34" s="13">
+        <v>9</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="K34" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="13">
+        <v>6</v>
+      </c>
+      <c r="C38" s="13">
+        <v>4</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="K38" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="13">
+        <v>5</v>
+      </c>
+      <c r="C39" s="13">
+        <v>3</v>
+      </c>
+      <c r="D39" s="13">
+        <v>1</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="K39" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="13">
+        <v>6</v>
+      </c>
+      <c r="C40" s="13">
+        <v>4</v>
+      </c>
+      <c r="D40" s="13">
+        <v>1</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="K40" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="13">
+        <v>4</v>
+      </c>
+      <c r="C41" s="13">
+        <v>2</v>
+      </c>
+      <c r="D41" s="13">
+        <v>1</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="K41" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="13">
+        <v>3</v>
+      </c>
+      <c r="C42" s="13">
+        <v>2</v>
+      </c>
+      <c r="D42" s="13">
+        <v>1</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="K42" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A11" location="Главная!B2" display="Э1" xr:uid="{EAD92861-D152-427C-80AB-912B7F3F3CB3}"/>
+    <hyperlink ref="A14" location="Главная!F9" display="А1" xr:uid="{1766066F-31AE-4767-9B8A-558B9E9E9FDF}"/>
+    <hyperlink ref="A15" location="Главная!F10" display="А2" xr:uid="{100D8117-E2D1-4872-B67C-FA5CC9644395}"/>
+    <hyperlink ref="A16" location="Главная!F11" display="А3" xr:uid="{77201C34-C015-4E4C-8460-EA448F09F944}"/>
+    <hyperlink ref="A17" location="Главная!F12" display="А4" xr:uid="{AAF1AD9E-738B-4066-B24B-88CE2A683DCD}"/>
+    <hyperlink ref="A18" location="Главная!F13" display="А5" xr:uid="{4227B6BE-C189-463D-9031-1F96F479A1A1}"/>
+    <hyperlink ref="A12" location="Главная!A9" display="С1" xr:uid="{599AC069-1B10-4FA2-9152-D44528C2CE6D}"/>
+    <hyperlink ref="A22" location="Главная!F9" display="А1" xr:uid="{1E3623CA-FED1-42B3-8EC9-8884A606EB67}"/>
+    <hyperlink ref="A23" location="Главная!F10" display="А2" xr:uid="{5BC0D3F6-6C41-45D0-8288-E60AF405C415}"/>
+    <hyperlink ref="A24" location="Главная!F11" display="А3" xr:uid="{83100C29-19DA-4A34-A9D2-BDE2C9FDC396}"/>
+    <hyperlink ref="A25" location="Главная!F12" display="А4" xr:uid="{17CA2E19-983B-489F-80A4-3A90438015AE}"/>
+    <hyperlink ref="A26" location="Главная!F13" display="А5" xr:uid="{B61FCB2F-202A-43B2-A487-4B02E7D32E6A}"/>
+    <hyperlink ref="A20" location="Главная!A10" display="С2" xr:uid="{F5EE3E81-F22D-419F-8793-191DD47F3CE7}"/>
+    <hyperlink ref="A30" location="Главная!F9" display="А1" xr:uid="{2DD42B7F-FC41-4707-B943-D8078354B4EA}"/>
+    <hyperlink ref="A31" location="Главная!F10" display="А2" xr:uid="{84C27154-9B17-4FA0-92F7-38448284197E}"/>
+    <hyperlink ref="A32" location="Главная!F11" display="А3" xr:uid="{1A4C76EA-4EC0-473F-A8A4-A7A91DD83D54}"/>
+    <hyperlink ref="A33" location="Главная!F12" display="А4" xr:uid="{3BDC58A0-E8EB-47A5-A0A6-ACBEBE31FBBE}"/>
+    <hyperlink ref="A34" location="Главная!F13" display="А5" xr:uid="{F353EA1A-E45D-4AF4-AA1F-B70D2E6096A7}"/>
+    <hyperlink ref="A28" location="Главная!A11" display="С3" xr:uid="{2AF42143-10EC-486A-B80F-94786D4C5D60}"/>
+    <hyperlink ref="A38" location="Главная!F9" display="А1" xr:uid="{1EEC1B3C-F84C-4071-AEE8-EC1EBFAF0C0F}"/>
+    <hyperlink ref="A39" location="Главная!F10" display="А2" xr:uid="{3FC06038-5FE8-4D92-B038-4682F7A7D6C5}"/>
+    <hyperlink ref="A40" location="Главная!F11" display="А3" xr:uid="{D68A431C-DC02-471F-BB52-72EAB2C20954}"/>
+    <hyperlink ref="A41" location="Главная!F12" display="А4" xr:uid="{49B0CFE1-4384-4D18-AD22-495710199661}"/>
+    <hyperlink ref="A42" location="Главная!F13" display="А5" xr:uid="{A7B956EA-0F9E-4852-B6E8-6D2DF5BECE2E}"/>
+    <hyperlink ref="A36" location="Главная!A12" display="С4" xr:uid="{E095B465-AB29-4DFF-BDEB-C4C22B5042A8}"/>
+    <hyperlink ref="F11" location="Главная!B3" display="Э2" xr:uid="{FFEE6135-B71C-4E50-89B7-89DB682DAE96}"/>
+    <hyperlink ref="F14" location="Главная!F9" display="А1" xr:uid="{C700A738-22B7-4466-9DCF-9BD8DFFBA0E6}"/>
+    <hyperlink ref="F15" location="Главная!F10" display="А2" xr:uid="{2B5A92C9-0248-46F5-99A5-EC70A4E4FF14}"/>
+    <hyperlink ref="F16" location="Главная!F11" display="А3" xr:uid="{C78818D3-1929-4C9E-BED5-96E9114CB024}"/>
+    <hyperlink ref="F17" location="Главная!F12" display="А4" xr:uid="{1D728B25-5EA6-449C-A83F-8583DDD3CE93}"/>
+    <hyperlink ref="F18" location="Главная!F13" display="А5" xr:uid="{CD66D9AD-FBC3-45AB-AAA3-8380B8CF1D07}"/>
+    <hyperlink ref="F12" location="Главная!A9" display="С1" xr:uid="{9D2953F9-8956-4B22-983F-819E823875B3}"/>
+    <hyperlink ref="F22" location="Главная!F9" display="А1" xr:uid="{6BE75BA5-6FDD-44B7-A78E-26E9412F5653}"/>
+    <hyperlink ref="F23" location="Главная!F10" display="А2" xr:uid="{14C90F36-2B04-4341-8181-07560402CE8B}"/>
+    <hyperlink ref="F24" location="Главная!F11" display="А3" xr:uid="{2F024564-54AA-49E9-9EA6-3E8974D07D4F}"/>
+    <hyperlink ref="F25" location="Главная!F12" display="А4" xr:uid="{34A86A65-738F-45A8-A20D-2143887747C0}"/>
+    <hyperlink ref="F26" location="Главная!F13" display="А5" xr:uid="{25B32627-63EE-4C1E-AA26-03848FBC33F9}"/>
+    <hyperlink ref="F20" location="Главная!A10" display="С2" xr:uid="{469CAEE1-02DC-41D2-B92A-949916D91653}"/>
+    <hyperlink ref="F30" location="Главная!F9" display="А1" xr:uid="{F77D8F34-490B-4899-AA85-D0F7695A807E}"/>
+    <hyperlink ref="F31" location="Главная!F10" display="А2" xr:uid="{8CACF4A5-7EF3-4ED0-850F-99001B366DD4}"/>
+    <hyperlink ref="F32" location="Главная!F11" display="А3" xr:uid="{45F467A3-8D48-4E27-93BE-7D183A898D2F}"/>
+    <hyperlink ref="F33" location="Главная!F12" display="А4" xr:uid="{89E7565E-F0F7-4509-A2F0-A481EEA5F88E}"/>
+    <hyperlink ref="F34" location="Главная!F13" display="А5" xr:uid="{51A42CD7-6E91-4D73-9E01-A4906639EA88}"/>
+    <hyperlink ref="F28" location="Главная!A11" display="С3" xr:uid="{9AD85F30-7800-4CAF-86FE-24BB27424554}"/>
+    <hyperlink ref="F38" location="Главная!F9" display="А1" xr:uid="{7A9D90FF-8B7C-42BA-8DBF-D94146C53DAF}"/>
+    <hyperlink ref="F39" location="Главная!F10" display="А2" xr:uid="{50007130-7FF4-4D9C-AE94-075BAC7402E2}"/>
+    <hyperlink ref="F40" location="Главная!F11" display="А3" xr:uid="{BC80BBDE-6C32-4E8B-B17C-B98B8B8BB754}"/>
+    <hyperlink ref="F41" location="Главная!F12" display="А4" xr:uid="{62CB1661-181F-4398-A99B-AFE49137B7EE}"/>
+    <hyperlink ref="F42" location="Главная!F13" display="А5" xr:uid="{EA33C30F-4BED-48F2-A7CE-DA258C7233DF}"/>
+    <hyperlink ref="F36" location="Главная!A12" display="С4" xr:uid="{C0E10753-F38D-4580-A6EC-34155E02C389}"/>
+    <hyperlink ref="K11" location="Главная!B4" display="Э3" xr:uid="{E800CC34-8689-49F9-8E89-DE6B41C5D523}"/>
+    <hyperlink ref="K14" location="Главная!F9" display="А1" xr:uid="{D13678BE-FF53-41F1-9A20-5D9570185013}"/>
+    <hyperlink ref="K15" location="Главная!F10" display="А2" xr:uid="{9470AFC5-5B11-4BF4-83D7-AF4A81BAF892}"/>
+    <hyperlink ref="K16" location="Главная!F11" display="А3" xr:uid="{D4A668F9-D300-435C-8135-F8253D4736F2}"/>
+    <hyperlink ref="K17" location="Главная!F12" display="А4" xr:uid="{9340E70E-3D77-4A3B-8081-AB9A0856F773}"/>
+    <hyperlink ref="K18" location="Главная!F13" display="А5" xr:uid="{8E684103-EA4E-4CC8-B013-D283B6A6E823}"/>
+    <hyperlink ref="K12" location="Главная!A9" display="С1" xr:uid="{80EE3F5A-D662-4E15-9E24-D0817B3B944F}"/>
+    <hyperlink ref="K22" location="Главная!F9" display="А1" xr:uid="{C3725B8C-D40F-4163-BCCD-E2B63E3F2847}"/>
+    <hyperlink ref="K23" location="Главная!F10" display="А2" xr:uid="{6CF4D914-1501-41ED-90E9-263CD0DED208}"/>
+    <hyperlink ref="K24" location="Главная!F11" display="А3" xr:uid="{ACAFBB0B-2B16-4A0F-AD1D-6FC29B3FD720}"/>
+    <hyperlink ref="K25" location="Главная!F12" display="А4" xr:uid="{4673A23C-E8A0-47D9-94CE-3795BBB6CD06}"/>
+    <hyperlink ref="K26" location="Главная!F13" display="А5" xr:uid="{D88F36D1-CDB2-4B2F-AB86-6CC00ED2ECA8}"/>
+    <hyperlink ref="K20" location="Главная!A10" display="С2" xr:uid="{921F2A2F-60D9-4959-A325-46AE3650C76F}"/>
+    <hyperlink ref="K30" location="Главная!F9" display="А1" xr:uid="{4CAFB7AB-97B0-4065-98DA-B0049BAB6139}"/>
+    <hyperlink ref="K31" location="Главная!F10" display="А2" xr:uid="{2C96D57C-6466-4501-8B32-3CABEEDE1B86}"/>
+    <hyperlink ref="K32" location="Главная!F11" display="А3" xr:uid="{2E8DC128-1F7D-44FE-B2CE-25066FA022D1}"/>
+    <hyperlink ref="K33" location="Главная!F12" display="А4" xr:uid="{C13FA7A3-B9F6-471F-B366-A44B80D32169}"/>
+    <hyperlink ref="K34" location="Главная!F13" display="А5" xr:uid="{3C58F1F6-7F88-459D-8AB2-BCFBA15409E7}"/>
+    <hyperlink ref="K28" location="Главная!A11" display="С3" xr:uid="{30EECE43-AB2F-481E-A9E8-A37C337BD44C}"/>
+    <hyperlink ref="K38" location="Главная!F9" display="А1" xr:uid="{91DFAE90-F634-4E2C-BD32-2AFDC7B293E4}"/>
+    <hyperlink ref="K39" location="Главная!F10" display="А2" xr:uid="{2495B1DE-73CC-42DF-8781-5912D8C526A7}"/>
+    <hyperlink ref="K40" location="Главная!F11" display="А3" xr:uid="{A4BDDB20-4E3A-4D29-9E54-E4CAB6493A3B}"/>
+    <hyperlink ref="K41" location="Главная!F12" display="А4" xr:uid="{7B0B9738-0CE8-4EFA-8033-E91A4FD1D40E}"/>
+    <hyperlink ref="K42" location="Главная!F13" display="А5" xr:uid="{EF66AEB3-321C-4E1C-B25F-51D4F488D5BE}"/>
+    <hyperlink ref="K36" location="Главная!A12" display="С4" xr:uid="{29566E89-A0A8-477E-A5B7-7E4B39BCC557}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43E5DDF-1784-4B57-95E0-BC2B31D03D48}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/phase-1/TOPSIS.xlsx
+++ b/phase-1/TOPSIS.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6776008-8A5F-4006-82EB-492276D3DB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Главная" sheetId="1" r:id="rId1"/>
@@ -765,7 +765,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>25</v>
       </c>
@@ -773,7 +773,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
